--- a/extenbooks/S516.xlsx
+++ b/extenbooks/S516.xlsx
@@ -447,11 +447,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,6 +467,16 @@
           <t>S&amp;T 1994, units=thousands</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>, units=thousands</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>derived, units=thousands</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -475,6 +487,16 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>S516-A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S516-COMBINED</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>S516-EXT</t>
         </is>
       </c>
     </row>
@@ -485,6 +507,12 @@
       <c r="B3" s="3" t="n">
         <v>36154</v>
       </c>
+      <c r="C3" s="3" t="n">
+        <v>36154</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -493,6 +521,12 @@
       <c r="B4" s="3" t="n">
         <v>36642</v>
       </c>
+      <c r="C4" s="3" t="n">
+        <v>36642</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -501,6 +535,12 @@
       <c r="B5" s="3" t="n">
         <v>37594</v>
       </c>
+      <c r="C5" s="3" t="n">
+        <v>37594</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -509,6 +549,12 @@
       <c r="B6" s="3" t="n">
         <v>38763</v>
       </c>
+      <c r="C6" s="3" t="n">
+        <v>38763</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -517,6 +563,12 @@
       <c r="B7" s="3" t="n">
         <v>40735</v>
       </c>
+      <c r="C7" s="3" t="n">
+        <v>40735</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -525,6 +577,12 @@
       <c r="B8" s="3" t="n">
         <v>42281</v>
       </c>
+      <c r="C8" s="3" t="n">
+        <v>42281</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -533,6 +591,12 @@
       <c r="B9" s="3" t="n">
         <v>43484</v>
       </c>
+      <c r="C9" s="3" t="n">
+        <v>43484</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -541,6 +605,12 @@
       <c r="B10" s="3" t="n">
         <v>44750</v>
       </c>
+      <c r="C10" s="3" t="n">
+        <v>44750</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -549,6 +619,12 @@
       <c r="B11" s="3" t="n">
         <v>45028</v>
       </c>
+      <c r="C11" s="3" t="n">
+        <v>45028</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -557,6 +633,12 @@
       <c r="B12" s="3" t="n">
         <v>45210</v>
       </c>
+      <c r="C12" s="3" t="n">
+        <v>45210</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -565,6 +647,12 @@
       <c r="B13" s="3" t="n">
         <v>45960</v>
       </c>
+      <c r="C13" s="3" t="n">
+        <v>45960</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -573,6 +661,12 @@
       <c r="B14" s="3" t="n">
         <v>47837</v>
       </c>
+      <c r="C14" s="3" t="n">
+        <v>47837</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -581,6 +675,12 @@
       <c r="B15" s="3" t="n">
         <v>48955</v>
       </c>
+      <c r="C15" s="3" t="n">
+        <v>48955</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -588,6 +688,502 @@
       </c>
       <c r="B16" s="3" t="n">
         <v>49212</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>49212</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>51636.89791783905</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>51636.89791783905</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>52621.646370287</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>52621.646370287</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>53437.68564997186</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>53437.68564997186</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>54925.73353967361</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>54925.73353967361</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>56822.54845244795</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>56822.54845244795</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>58913.01440630276</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>58913.01440630276</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>60821.79110861001</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>60821.79110861001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>62932.84558244232</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>62932.84558244232</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>65180.78981429376</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>65180.78981429376</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>67737.30534608892</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>67737.30534608892</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>69813.17203151379</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>69813.17203151379</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>71154.4718064153</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>71154.4718064153</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>71753.96257737759</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>71753.96257737759</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>72884.3530669668</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>72884.3530669668</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>74082.34395047833</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>74082.34395047833</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>75424.62464828361</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>75424.62464828361</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>76717.13314575127</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>76717.13314575127</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>78380.48564997186</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>78380.48564997186</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>78904.36100168823</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>78904.36100168823</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>78223.81772650534</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>78223.81772650534</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>78746.76420934159</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>78746.76420934159</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>80205.01271806416</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>80205.01271806416</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>81975.22357906583</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>81975.22357906583</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>83817.27169386606</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>83817.27169386606</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>85496.21716375914</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>85496.21716375914</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>87590.13286437817</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>87590.13286437817</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>89749.58947664604</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>89749.58947664604</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>91378.29116488463</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>91378.29116488463</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>92578.64316263364</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>92578.64316263364</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>93981.47236916151</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>93981.47236916151</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>87839.99673607203</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>87839.99673607203</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>91322.677039955</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>91322.677039955</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>95804.16235227912</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>95804.16235227912</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>97966.272144063</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>97966.272144063</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>99244.64074282497</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>99244.64074282497</v>
       </c>
     </row>
   </sheetData>
@@ -601,7 +1197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -700,7 +1296,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948–2024</t>
+          <t>1948-1961</t>
         </is>
       </c>
     </row>
@@ -724,7 +1320,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fig_5_2, Fig_5_7</t>
+          <t>Fig_5_2, Fig_5_7, Fig_5_8</t>
         </is>
       </c>
     </row>
@@ -766,166 +1362,175 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S516-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S516-EXT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S516-COMBINED</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S516 — Unproductive Employment (Lu = L - Lp), narrow classification</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Source Table**: Appendix E.3, p. 320, rows `L_total` and `Lp_total`</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: thousands of workers</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Period**: 1948-1961</t>
+          <t># S516 — Unproductive Employment (Lu = L - Lp), narrow classification</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>**Content Type**: derived</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Status**: book_period_partial_1948_1961</t>
+          <t>**Chapter**: 5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Source Table**: Appendix E.3, p. 320, rows `L_total` and `Lp_total`</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Units**: thousands of workers</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Period**: 1948-1961</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Unproductive labor headcount, computed as the residual: Lu = L_total - Lp_total. Uses the same narrow classification as S515 (TableE3 source).</t>
+          <t>**Content Type**: derived</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_partial_1948_1961</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>## Source / Construction</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>No separate L01 loader. The P02 processor reads `TableE3_LaborStatistics.csv` directly, extracts the `L_total` and `Lp_total` rows, and computes Lu year-by-year. Both rows are pre-existing in the book table; no extrapolation.</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unproductive labor headcount, computed as the residual: Lu = L_total - Lp_total. Uses the same narrow classification as S515 (TableE3 source).</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>## Reference</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>## Source / Construction</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Validation benchmarks computed directly from the E.3 row values:</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>- 1948 = 66,091 - 29,937 = 36,154 thousand</t>
+          <t>No separate L01 loader. The P02 processor reads `TableE3_LaborStatistics.csv` directly, extracts the `L_total` and `Lp_total` rows, and computes Lu year-by-year. Both rows are pre-existing in the book table; no extrapolation.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>- 1961 = 82,827 - 33,615 = 49,212 thousand</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Validator PASS.</t>
+          <t>## Reference</t>
         </is>
       </c>
     </row>
@@ -937,41 +1542,77 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>## Coverage Caveat</t>
+          <t>Validation benchmarks computed directly from the E.3 row values:</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>- 1948 = 66,091 - 29,937 = 36,154 thousand</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Same as S515: 14-year coverage from salvaged E.3 only.</t>
+          <t>- 1961 = 82,827 - 33,615 = 49,212 thousand</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Validator PASS.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>## Coverage Caveat</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
+      <c r="B46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Same as S515: 14-year coverage from salvaged E.3 only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch).*</t>
         </is>
@@ -988,10 +1629,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1016,218 +1657,368 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lu = L - Lp. Unproductive employment is the residual of total employment minus productive employment. Unproductive sectors include trade (all), FIRE (mostly), services, and government. Lu has grown secularly both in absolute terms and as a share of total employment.</t>
+          <t>Lu = L - Lp = total unproductive labor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_15/full_transcription.md</t>
+          <t>ST_1994, p. 109, Section 5.3 notation block</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Derived from total employment (L, from BLS) minus S515 (Lp). Book period from Table E.3 (chunk_30). Extension follows directly from S515 extension: Lu = L_total - Lp_extended.</t>
+          <t>Productive labor is the production labor employed in capitalist production sectors: agriculture, mining, construction, transportation and public utilities, manufacturing, and productive services (defined as all services except business services, legal services, and private households, as in Table E.1).</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_13/full_transcription.md; BLS</t>
+          <t>ST_1994, pp. 108-109, Section 5.3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fig 5.2 shows Lu rising over time as the economy shifts toward services and finance. Fig 5.7 shows the employment composition with Lu's growing dominance, illustrating the structural transformation of US employment.</t>
+          <t>Figures 5.10 and 5.11 make quite explicit that the unit wages of productive and unproductive workers change only slightly, whereas their relative employments change drastically. We can therefore unambiguously conclude that the relative decline in productive to total wages Wp/W (= V*/W) is almost entirely due to the relative decline in productive to total employment Lp/L.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Figs 5.2, 5.7; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_14/full_transcription.md</t>
+          <t>ST_1994, p. 113, Section 5.3 empirical results summary</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>theoretical_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unproductive labor does not create new value but performs necessary functions for value realization, distribution, and social reproduction. The growth of Lu is theoretically significant because these workers are paid out of surplus value, increasing the burden on productive workers.</t>
+          <t>Total unproductive labor = nonproduction workers in production sectors + all workers in nonproduction sectors</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 pp.230-235; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_16/full_transcription.md</t>
+          <t>ST_1994, p. 109, Section 5.3 textual definition</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>external_comparison</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mohun (2013) further decomposes unproductive labor into Luw (unproductive wage workers) and Lum (unproductive management/supervisory). This decomposition reveals that within Lu, managerial employment has grown disproportionately. See mohun_employment*.csv and mohun_unproductive_decomposition*.csv.</t>
+          <t>Lu = L − Lp = total unproductive labor.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mohun_2013; Inputs/ExternalSources/Mohun/</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sector_classification</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Industry productive/unproductive assignments per Appendix B (chunk_27): Trade fully unproductive; FIRE decomposed with real estate entirely unproductive; government wages classified as unproductive unless in government enterprises. The 64-industry SIC classification in Appendix B is the definitive reference.</t>
+          <t>Total unproductive labor = nonproduction workers in production sectors + all workers in nonproduction sectors.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_27/full_transcription.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>As a residual series, Lu inherits all measurement issues from S515. Any overcount in Lp leads to undercount in Lu and vice versa. The classification of entire sectors as unproductive (especially all of trade) is the most debated aspect of ST's methodology.</t>
+          <t>Footnote 7: Notes asymmetry between production and nonproduction sectors: Production sectors always have nonproduction activities (buying, selling, finance); Nonproduction sectors have no systematic reason to incorporate production activities. Data limitations prevent further breakdown of nonproduction sectors.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DPR T516_DPR.md; EPR T516_EPR.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>methodology_description</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Lu = L - Lp. Unproductive employment is the residual of total employment minus productive employment. Unproductive sectors include trade (all), FIRE (mostly), services, and government. Lu has grown secularly both in absolute terms and as a share of total employment.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_15/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>data_source</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unproductive employment Lu = L - Lp. Residual series derived from S515. Shows secular growth reflecting shift to services, FIRE, and government. Mohun provides Luw/Lum decomposition. Industry classifications per Appendix B (chunk_27).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+          <t>Derived from total employment (L, from BLS) minus S515 (Lp). Book period from Table E.3 (chunk_30). Extension follows directly from S515 extension: Lu = L_total - Lp_extended.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_13/full_transcription.md; BLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>figure_context</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fig 5.2 shows Lu rising over time as the economy shifts toward services and finance. Fig 5.7 shows the employment composition with Lu's growing dominance, illustrating the structural transformation of US employment.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Figs 5.2, 5.7; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_14/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>theoretical_note</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Unproductive labor does not create new value but performs necessary functions for value realization, distribution, and social reproduction. The growth of Lu is theoretically significant because these workers are paid out of surplus value, increasing the burden on productive workers.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 pp.230-235; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_16/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>external_comparison</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Residual series — inherits all S515 measurement issues</t>
+          <t>Mohun (2013) further decomposes unproductive labor into Luw (unproductive wage workers) and Lum (unproductive management/supervisory). This decomposition reveals that within Lu, managerial employment has grown disproportionately. See mohun_employment*.csv and mohun_unproductive_decomposition*.csv.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mohun_2013; Inputs/ExternalSources/Mohun/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sector_classification</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Trade classified entirely as unproductive — debatable</t>
+          <t>Industry productive/unproductive assignments per Appendix B (chunk_27): Trade fully unproductive; FIRE decomposed with real estate entirely unproductive; government wages classified as unproductive unless in government enterprises. The 64-industry SIC classification in Appendix B is the definitive reference.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_27/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mohun's Luw/Lum decomposition reveals heterogeneity within Lu</t>
+          <t>As a residual series, Lu inherits all measurement issues from S515. Any overcount in Lp leads to undercount in Lu and vice versa. The classification of entire sectors as unproductive (especially all of trade) is the most debated aspect of ST's methodology.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DPR T516_DPR.md; EPR T516_EPR.md</t>
         </is>
       </c>
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>S511</t>
-        </is>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>109</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>S515</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Unproductive employment Lu = L - Lp. Residual series derived from S515. Shows secular growth reflecting shift to services, FIRE, and government. Mohun provides Luw/Lum decomposition. Industry classifications per Appendix B (chunk_27).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Residual series — inherits all S515 measurement issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Trade classified entirely as unproductive — debatable</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Mohun's Luw/Lum decomposition reveals heterogeneity within Lu</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>S511</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S515</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Mohun_2013</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Mohun, Simon. 2013. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379.</t>
         </is>
@@ -1244,11 +2035,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1348,91 +2139,178 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>splice_year</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>BLS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>splice_method</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>derive</t>
+          <t>1989</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>['S515']</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>derive</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>output_subseries</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S516-EXT</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>combined_subseries</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S516-COMBINED</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>provenance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5, identity Lu = L - Lp (unproductive employment = total - productive); Appendix E.3 / Table 5.7", "shaikh_appendix_ref": "Derived identity from S515 (Lp) and total employment L; Table 5.7 column complementary to Lp/L", "extension_source": "Derived: Lu = L_total - S515. Total employment L from BLS CES total nonfarm payrolls.", "extension_url": "https://www.bls.gov/ces/ (CES total nonfarm employment)", "conceptual_continuity": "Unproductive Employment Lu is the count of workers in unproductive sectors (trade, finance, government services, etc.) under Appendix C. It is a derived identity Lu = L - Lp, and the extension is mechanical once S515 (Lp) and total employment L are extended.", "vintage_note": "Inherits all vintage divergences from S515 (Appendix C update for NAICS, BLS CES 2003 overhaul, KB coverage gap 1962-1989).", "note": "Hyper-review cleanup 2026-05-19 per Decision 0003"}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>["S515"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>{"1948": 36154.0, "1961": 49212.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>expected_range</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>[10000, 200000]</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>tolerance</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>level_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>level_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>10.0</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S516.xlsx
+++ b/extenbooks/S516.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -505,10 +505,10 @@
         <v>1948</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>36154</v>
+        <v>25307</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>36154</v>
+        <v>25307</v>
       </c>
       <c r="D3" s="3" t="n">
         <v/>
@@ -519,10 +519,10 @@
         <v>1949</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>36642</v>
+        <v>25718</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>36642</v>
+        <v>25718</v>
       </c>
       <c r="D4" s="3" t="n">
         <v/>
@@ -533,10 +533,10 @@
         <v>1950</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>37594</v>
+        <v>26374</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>37594</v>
+        <v>26374</v>
       </c>
       <c r="D5" s="3" t="n">
         <v/>
@@ -547,10 +547,10 @@
         <v>1951</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>38763</v>
+        <v>29243</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>38763</v>
+        <v>29243</v>
       </c>
       <c r="D6" s="3" t="n">
         <v/>
@@ -561,10 +561,10 @@
         <v>1952</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>40735</v>
+        <v>30689</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>40735</v>
+        <v>30689</v>
       </c>
       <c r="D7" s="3" t="n">
         <v/>
@@ -575,10 +575,10 @@
         <v>1953</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>42281</v>
+        <v>31204</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>42281</v>
+        <v>31204</v>
       </c>
       <c r="D8" s="3" t="n">
         <v/>
@@ -589,10 +589,10 @@
         <v>1954</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>43484</v>
+        <v>31094</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>43484</v>
+        <v>31094</v>
       </c>
       <c r="D9" s="3" t="n">
         <v/>
@@ -603,10 +603,10 @@
         <v>1955</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>44750</v>
+        <v>31652</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>44750</v>
+        <v>31652</v>
       </c>
       <c r="D10" s="3" t="n">
         <v/>
@@ -617,10 +617,10 @@
         <v>1956</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>45028</v>
+        <v>32658</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>45028</v>
+        <v>32658</v>
       </c>
       <c r="D11" s="3" t="n">
         <v/>
@@ -631,10 +631,10 @@
         <v>1957</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>45210</v>
+        <v>33346</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>45210</v>
+        <v>33346</v>
       </c>
       <c r="D12" s="3" t="n">
         <v/>
@@ -645,10 +645,10 @@
         <v>1958</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>45960</v>
+        <v>33416</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>45960</v>
+        <v>33416</v>
       </c>
       <c r="D13" s="3" t="n">
         <v/>
@@ -659,10 +659,10 @@
         <v>1959</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>47837</v>
+        <v>34079</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>47837</v>
+        <v>34079</v>
       </c>
       <c r="D14" s="3" t="n">
         <v/>
@@ -673,10 +673,10 @@
         <v>1960</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>48955</v>
+        <v>34942</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>48955</v>
+        <v>34942</v>
       </c>
       <c r="D15" s="3" t="n">
         <v/>
@@ -687,10 +687,10 @@
         <v>1961</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>49212</v>
+        <v>35377</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>49212</v>
+        <v>35377</v>
       </c>
       <c r="D16" s="3" t="n">
         <v/>
@@ -698,492 +698,884 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1990</v>
+        <v>1962</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v/>
+        <v>36154</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>51636.89791783905</v>
+        <v>36154</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>51636.89791783905</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1991</v>
+        <v>1963</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v/>
+        <v>36642</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>52621.646370287</v>
+        <v>36642</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>52621.646370287</v>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1992</v>
+        <v>1964</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v/>
+        <v>37594</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>53437.68564997186</v>
+        <v>37594</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>53437.68564997186</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1993</v>
+        <v>1965</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v/>
+        <v>38763</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>54925.73353967361</v>
+        <v>38763</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>54925.73353967361</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1994</v>
+        <v>1966</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v/>
+        <v>40735</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>56822.54845244795</v>
+        <v>40735</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>56822.54845244795</v>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1995</v>
+        <v>1967</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v/>
+        <v>42281</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>58913.01440630276</v>
+        <v>42281</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>58913.01440630276</v>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1996</v>
+        <v>1968</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v/>
+        <v>43484</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>60821.79110861001</v>
+        <v>43484</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>60821.79110861001</v>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1997</v>
+        <v>1969</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v/>
+        <v>44750</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>62932.84558244232</v>
+        <v>44750</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>62932.84558244232</v>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1998</v>
+        <v>1970</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v/>
+        <v>45028</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>65180.78981429376</v>
+        <v>45028</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>65180.78981429376</v>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1999</v>
+        <v>1971</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v/>
+        <v>45210</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>67737.30534608892</v>
+        <v>45210</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>67737.30534608892</v>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2000</v>
+        <v>1972</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v/>
+        <v>45960</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>69813.17203151379</v>
+        <v>45960</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>69813.17203151379</v>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2001</v>
+        <v>1973</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v/>
+        <v>47837</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>71154.4718064153</v>
+        <v>47837</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>71154.4718064153</v>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2002</v>
+        <v>1974</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v/>
+        <v>48955</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>71753.96257737759</v>
+        <v>48955</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>71753.96257737759</v>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2003</v>
+        <v>1975</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v/>
+        <v>49212</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>72884.3530669668</v>
+        <v>49212</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>72884.3530669668</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2004</v>
+        <v>1976</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v/>
+        <v>50474</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>74082.34395047833</v>
+        <v>50474</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>74082.34395047833</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2005</v>
+        <v>1977</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v/>
+        <v>52318</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>75424.62464828361</v>
+        <v>52318</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>75424.62464828361</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2006</v>
+        <v>1978</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v/>
+        <v>54929</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>76717.13314575127</v>
+        <v>54929</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>76717.13314575127</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2007</v>
+        <v>1979</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v/>
+        <v>56927</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>78380.48564997186</v>
+        <v>56927</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>78380.48564997186</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2008</v>
+        <v>1980</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v/>
+        <v>57871</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>78904.36100168823</v>
+        <v>57871</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>78904.36100168823</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2009</v>
+        <v>1981</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v/>
+        <v>58844</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>78223.81772650534</v>
+        <v>58844</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>78223.81772650534</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2010</v>
+        <v>1982</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v/>
+        <v>58787</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>78746.76420934159</v>
+        <v>58787</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>78746.76420934159</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2011</v>
+        <v>1983</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v/>
+        <v>59864</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>80205.01271806416</v>
+        <v>59864</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>80205.01271806416</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2012</v>
+        <v>1984</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v/>
+        <v>62735</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>81975.22357906583</v>
+        <v>62735</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>81975.22357906583</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2013</v>
+        <v>1985</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v/>
+        <v>64802</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>83817.27169386606</v>
+        <v>64802</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>83817.27169386606</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2014</v>
+        <v>1986</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v/>
+        <v>66519</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>85496.21716375914</v>
+        <v>66519</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>85496.21716375914</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2015</v>
+        <v>1987</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v/>
+        <v>68547</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>87590.13286437817</v>
+        <v>68547</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>87590.13286437817</v>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2016</v>
+        <v>1988</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v/>
+        <v>70424</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>89749.58947664604</v>
+        <v>70424</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>89749.58947664604</v>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2017</v>
+        <v>1989</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v/>
+        <v>72363</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>91378.29116488463</v>
+        <v>72363</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>91378.29116488463</v>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2018</v>
+        <v>1990</v>
       </c>
       <c r="B45" s="3" t="n">
         <v/>
       </c>
       <c r="C45" s="3" t="n">
-        <v>92578.64316263364</v>
+        <v>56630.37665213471</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>92578.64316263364</v>
+        <v>56630.37665213471</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2019</v>
+        <v>1991</v>
       </c>
       <c r="B46" s="3" t="n">
         <v/>
       </c>
       <c r="C46" s="3" t="n">
-        <v>93981.47236916151</v>
+        <v>57335.4849909486</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>93981.47236916151</v>
+        <v>57335.4849909486</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2020</v>
+        <v>1992</v>
       </c>
       <c r="B47" s="3" t="n">
         <v/>
       </c>
       <c r="C47" s="3" t="n">
-        <v>87839.99673607203</v>
+        <v>58063.27907601141</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>87839.99673607203</v>
+        <v>58063.27907601141</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2021</v>
+        <v>1993</v>
       </c>
       <c r="B48" s="3" t="n">
         <v/>
       </c>
       <c r="C48" s="3" t="n">
-        <v>91322.677039955</v>
+        <v>59607.77390823847</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>91322.677039955</v>
+        <v>59607.77390823847</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2022</v>
+        <v>1994</v>
       </c>
       <c r="B49" s="3" t="n">
         <v/>
       </c>
       <c r="C49" s="3" t="n">
-        <v>95804.16235227912</v>
+        <v>61665.79990507895</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>95804.16235227912</v>
+        <v>61665.79990507895</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2023</v>
+        <v>1995</v>
       </c>
       <c r="B50" s="3" t="n">
         <v/>
       </c>
       <c r="C50" s="3" t="n">
-        <v>97966.272144063</v>
+        <v>63854.11106982799</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>97966.272144063</v>
+        <v>63854.11106982799</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>65814.34731881943</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>65814.34731881943</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>68035.23981666678</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>68035.23981666678</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>70372.58239824802</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>70372.58239824802</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>72946.02048124971</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>72946.02048124971</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>75051.66739733273</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>75051.66739733273</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>76189.29115132449</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>76189.29115132449</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>76481.00482402316</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>76481.00482402316</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>77420.43282776576</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>77420.43282776576</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>78643.01474395048</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>78643.01474395048</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>80078.78749211816</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>80078.78749211816</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>81490.99348977226</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>81490.99348977226</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>83108.5369073367</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>83108.5369073367</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>83435.16507786915</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>83435.16507786915</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>82083.62967435301</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>82083.62967435301</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>82427.43351119729</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>82427.43351119729</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>83951.52717657348</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>83951.52717657348</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>85802.80484165135</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>85802.80484165135</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>87700.06025723602</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>87700.06025723602</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>89487.20050511556</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>89487.20050511556</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>91661.14517021376</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>91661.14517021376</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>93841.81983646459</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>93841.81983646459</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>95538.0675851408</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>95538.0675851408</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>96861.89366605418</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>96861.89366605418</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>98321.60224827276</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>98321.60224827276</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>91930.67033649512</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>91930.67033649512</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>95496.20483487129</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>95496.20483487129</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>100173.841831027</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>100173.841831027</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>102410.0994962404</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>102410.0994962404</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
         <v>2024</v>
       </c>
-      <c r="B51" s="3" t="n">
-        <v/>
-      </c>
-      <c r="C51" s="3" t="n">
-        <v>99244.64074282497</v>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>99244.64074282497</v>
+      <c r="B79" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>103682.096913032</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>103682.096913032</v>
       </c>
     </row>
   </sheetData>
@@ -1197,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1296,7 +1688,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948-1961</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1700,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>book_period_partial_1948_1961</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1862,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>**Status**: book_period_partial_1948_1961</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1874,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>&gt; **v1.3 note:** Status widened from `book_period_partial_1948_1961` to `book_period_validated`. The panel-backed rebuild (B6) supplies real book-arm data across the full book period 1948-1989 (previously partial 1948-1961); V03 PASS post-rebuild.</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1886,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Unproductive labor headcount, computed as the residual: Lu = L_total - Lp_total. Uses the same narrow classification as S515 (TableE3 source).</t>
+          <t>## Definition</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1898,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>## Source / Construction</t>
+          <t>Unproductive labor headcount, computed as the residual: Lu = L_total - Lp_total. Uses the same narrow classification as S515 (TableE3 source).</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1910,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>No separate L01 loader. The P02 processor reads `TableE3_LaborStatistics.csv` directly, extracts the `L_total` and `Lp_total` rows, and computes Lu year-by-year. Both rows are pre-existing in the book table; no extrapolation.</t>
+          <t>## Source / Construction</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1922,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>## Reference</t>
+          <t>No separate L01 loader. The P02 processor reads `TableE3_LaborStatistics.csv` directly, extracts the `L_total` and `Lp_total` rows, and computes Lu year-by-year. Both rows are pre-existing in the book table; no extrapolation.</t>
         </is>
       </c>
     </row>
@@ -1542,23 +1934,19 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Validation benchmarks computed directly from the E.3 row values:</t>
+          <t>## Reference</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>- 1948 = 66,091 - 29,937 = 36,154 thousand</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>- 1961 = 82,827 - 33,615 = 49,212 thousand</t>
+          <t>Validation benchmarks computed directly from the E.3 row values:</t>
         </is>
       </c>
     </row>
@@ -1566,19 +1954,23 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Validator PASS.</t>
+          <t>- 1948 = 66,091 - 29,937 = 36,154 thousand</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>- 1961 = 82,827 - 33,615 = 49,212 thousand</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>## Coverage Caveat</t>
+          <t>Validator PASS.</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1982,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Same as S515: 14-year coverage from salvaged E.3 only.</t>
+          <t>## Coverage Caveat</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1994,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Same as S515: 14-year coverage from salvaged E.3 only.</t>
         </is>
       </c>
     </row>
@@ -1613,6 +2005,18 @@
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch).*</t>
         </is>
@@ -2035,10 +2439,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2250,38 +2654,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{"1948": 36154.0, "1961": 49212.0}</t>
+          <t>{"1948": 25307.0, "1958": 33416.0, "1967": 42281.0, "1977": 52318.0, "1989": 72363.0}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>expected_range</t>
+          <t>v1.3_patch</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[10000, 200000]</t>
+          <t>DIV-014: replaced v1.2 refvals {1948:36154,1961:49212} (same 14-year misalignment of Lu) with book Table 5.5 'Lu=L-Lp' anchors. Identity-checked as L-Lp.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tolerance</t>
+          <t>expected_range</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>level_series</t>
+          <t>[10000, 200000]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tolerance_class</t>
+          <t>tolerance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2293,24 +2697,48 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tolerance_rel</t>
+          <t>tolerance_class</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>level_series</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>tolerance_abs</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>10.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>extension_year_range</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>[1948, 2024]</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S516.xlsx
+++ b/extenbooks/S516.xlsx
@@ -453,7 +453,7 @@
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,7 +474,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>derived, units=thousands</t>
+          <t>CES0000000001 re-anchored @1989 minus S515-EXT, units=thousands</t>
         </is>
       </c>
     </row>
@@ -1096,10 +1096,10 @@
         <v/>
       </c>
       <c r="C45" s="3" t="n">
-        <v>56630.37665213471</v>
+        <v>74222.2004084503</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>56630.37665213471</v>
+        <v>74222.2004084503</v>
       </c>
     </row>
     <row r="46">
@@ -1110,10 +1110,10 @@
         <v/>
       </c>
       <c r="C46" s="3" t="n">
-        <v>57335.4849909486</v>
+        <v>74414.95476697267</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>57335.4849909486</v>
+        <v>74414.95476697267</v>
       </c>
     </row>
     <row r="47">
@@ -1124,10 +1124,10 @@
         <v/>
       </c>
       <c r="C47" s="3" t="n">
-        <v>58063.27907601141</v>
+        <v>75076.10861993078</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>58063.27907601141</v>
+        <v>75076.10861993078</v>
       </c>
     </row>
     <row r="48">
@@ -1138,10 +1138,10 @@
         <v/>
       </c>
       <c r="C48" s="3" t="n">
-        <v>59607.77390823847</v>
+        <v>76743.30084081343</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>59607.77390823847</v>
+        <v>76743.30084081343</v>
       </c>
     </row>
     <row r="49">
@@ -1152,10 +1152,10 @@
         <v/>
       </c>
       <c r="C49" s="3" t="n">
-        <v>61665.79990507895</v>
+        <v>79132.97991328401</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>61665.79990507895</v>
+        <v>79132.97991328401</v>
       </c>
     </row>
     <row r="50">
@@ -1166,10 +1166,10 @@
         <v/>
       </c>
       <c r="C50" s="3" t="n">
-        <v>63854.11106982799</v>
+        <v>81434.99744428354</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>63854.11106982799</v>
+        <v>81434.99744428354</v>
       </c>
     </row>
     <row r="51">
@@ -1180,10 +1180,10 @@
         <v/>
       </c>
       <c r="C51" s="3" t="n">
-        <v>65814.34731881943</v>
+        <v>83390.76936256059</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>65814.34731881943</v>
+        <v>83390.76936256059</v>
       </c>
     </row>
     <row r="52">
@@ -1194,10 +1194,10 @@
         <v/>
       </c>
       <c r="C52" s="3" t="n">
-        <v>68035.23981666678</v>
+        <v>85721.848745551</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>68035.23981666678</v>
+        <v>85721.848745551</v>
       </c>
     </row>
     <row r="53">
@@ -1208,10 +1208,10 @@
         <v/>
       </c>
       <c r="C53" s="3" t="n">
-        <v>70372.58239824802</v>
+        <v>88201.80632977805</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>70372.58239824802</v>
+        <v>88201.80632977805</v>
       </c>
     </row>
     <row r="54">
@@ -1222,10 +1222,10 @@
         <v/>
       </c>
       <c r="C54" s="3" t="n">
-        <v>72946.02048124971</v>
+        <v>90859.75232907241</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>72946.02048124971</v>
+        <v>90859.75232907241</v>
       </c>
     </row>
     <row r="55">
@@ -1236,10 +1236,10 @@
         <v/>
       </c>
       <c r="C55" s="3" t="n">
-        <v>75051.66739733273</v>
+        <v>93170.44880669836</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>75051.66739733273</v>
+        <v>93170.44880669836</v>
       </c>
     </row>
     <row r="56">
@@ -1250,10 +1250,10 @@
         <v/>
       </c>
       <c r="C56" s="3" t="n">
-        <v>76189.29115132449</v>
+        <v>94042.12868349608</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>76189.29115132449</v>
+        <v>94042.12868349608</v>
       </c>
     </row>
     <row r="57">
@@ -1264,10 +1264,10 @@
         <v/>
       </c>
       <c r="C57" s="3" t="n">
-        <v>76481.00482402316</v>
+        <v>93993.06954558712</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>76481.00482402316</v>
+        <v>93993.06954558712</v>
       </c>
     </row>
     <row r="58">
@@ -1278,10 +1278,10 @@
         <v/>
       </c>
       <c r="C58" s="3" t="n">
-        <v>77420.43282776576</v>
+        <v>94533.28086955971</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>77420.43282776576</v>
+        <v>94533.28086955971</v>
       </c>
     </row>
     <row r="59">
@@ -1292,10 +1292,10 @@
         <v/>
       </c>
       <c r="C59" s="3" t="n">
-        <v>78643.01474395048</v>
+        <v>95716.6663074906</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>78643.01474395048</v>
+        <v>95716.6663074906</v>
       </c>
     </row>
     <row r="60">
@@ -1306,10 +1306,10 @@
         <v/>
       </c>
       <c r="C60" s="3" t="n">
-        <v>80078.78749211816</v>
+        <v>97332.33778325201</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>80078.78749211816</v>
+        <v>97332.33778325201</v>
       </c>
     </row>
     <row r="61">
@@ -1320,10 +1320,10 @@
         <v/>
       </c>
       <c r="C61" s="3" t="n">
-        <v>81490.99348977226</v>
+        <v>98965.71338474784</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>81490.99348977226</v>
+        <v>98965.71338474784</v>
       </c>
     </row>
     <row r="62">
@@ -1334,10 +1334,10 @@
         <v/>
       </c>
       <c r="C62" s="3" t="n">
-        <v>83108.5369073367</v>
+        <v>100521.6258342946</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>83108.5369073367</v>
+        <v>100521.6258342946</v>
       </c>
     </row>
     <row r="63">
@@ -1348,10 +1348,10 @@
         <v/>
       </c>
       <c r="C63" s="3" t="n">
-        <v>83435.16507786915</v>
+        <v>100649.2063967178</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>83435.16507786915</v>
+        <v>100649.2063967178</v>
       </c>
     </row>
     <row r="64">
@@ -1362,10 +1362,10 @@
         <v/>
       </c>
       <c r="C64" s="3" t="n">
-        <v>82083.62967435301</v>
+        <v>98208.21748478115</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>82083.62967435301</v>
+        <v>98208.21748478115</v>
       </c>
     </row>
     <row r="65">
@@ -1376,10 +1376,10 @@
         <v/>
       </c>
       <c r="C65" s="3" t="n">
-        <v>82427.43351119729</v>
+        <v>98142.11913245951</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>82427.43351119729</v>
+        <v>98142.11913245951</v>
       </c>
     </row>
     <row r="66">
@@ -1390,10 +1390,10 @@
         <v/>
       </c>
       <c r="C66" s="3" t="n">
-        <v>83951.52717657348</v>
+        <v>99340.76321847134</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>83951.52717657348</v>
+        <v>99340.76321847134</v>
       </c>
     </row>
     <row r="67">
@@ -1404,10 +1404,10 @@
         <v/>
       </c>
       <c r="C67" s="3" t="n">
-        <v>85802.80484165135</v>
+        <v>101031.13894095</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>85802.80484165135</v>
+        <v>101031.13894095</v>
       </c>
     </row>
     <row r="68">
@@ -1418,10 +1418,10 @@
         <v/>
       </c>
       <c r="C68" s="3" t="n">
-        <v>87700.06025723602</v>
+        <v>102790.2195984119</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>87700.06025723602</v>
+        <v>102790.2195984119</v>
       </c>
     </row>
     <row r="69">
@@ -1432,10 +1432,10 @@
         <v/>
       </c>
       <c r="C69" s="3" t="n">
-        <v>89487.20050511556</v>
+        <v>104625.2449446774</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>89487.20050511556</v>
+        <v>104625.2449446774</v>
       </c>
     </row>
     <row r="70">
@@ -1446,10 +1446,10 @@
         <v/>
       </c>
       <c r="C70" s="3" t="n">
-        <v>91661.14517021376</v>
+        <v>106848.9838517615</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>91661.14517021376</v>
+        <v>106848.9838517615</v>
       </c>
     </row>
     <row r="71">
@@ -1460,10 +1460,10 @@
         <v/>
       </c>
       <c r="C71" s="3" t="n">
-        <v>93841.81983646459</v>
+        <v>109005.1449742442</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>93841.81983646459</v>
+        <v>109005.1449742442</v>
       </c>
     </row>
     <row r="72">
@@ -1474,10 +1474,10 @@
         <v/>
       </c>
       <c r="C72" s="3" t="n">
-        <v>95538.0675851408</v>
+        <v>110747.18357218</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>95538.0675851408</v>
+        <v>110747.18357218</v>
       </c>
     </row>
     <row r="73">
@@ -1488,10 +1488,10 @@
         <v/>
       </c>
       <c r="C73" s="3" t="n">
-        <v>96861.89366605418</v>
+        <v>112254.7101265454</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>96861.89366605418</v>
+        <v>112254.7101265454</v>
       </c>
     </row>
     <row r="74">
@@ -1502,10 +1502,10 @@
         <v/>
       </c>
       <c r="C74" s="3" t="n">
-        <v>98321.60224827276</v>
+        <v>113796.3465040405</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>98321.60224827276</v>
+        <v>113796.3465040405</v>
       </c>
     </row>
     <row r="75">
@@ -1516,10 +1516,10 @@
         <v/>
       </c>
       <c r="C75" s="3" t="n">
-        <v>91930.67033649512</v>
+        <v>107095.3217231467</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>91930.67033649512</v>
+        <v>107095.3217231467</v>
       </c>
     </row>
     <row r="76">
@@ -1530,10 +1530,10 @@
         <v/>
       </c>
       <c r="C76" s="3" t="n">
-        <v>95496.20483487129</v>
+        <v>110449.515404268</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>95496.20483487129</v>
+        <v>110449.515404268</v>
       </c>
     </row>
     <row r="77">
@@ -1544,10 +1544,10 @@
         <v/>
       </c>
       <c r="C77" s="3" t="n">
-        <v>100173.841831027</v>
+        <v>115206.7960863524</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>100173.841831027</v>
+        <v>115206.7960863524</v>
       </c>
     </row>
     <row r="78">
@@ -1558,10 +1558,10 @@
         <v/>
       </c>
       <c r="C78" s="3" t="n">
-        <v>102410.0994962404</v>
+        <v>117810.5491857671</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>102410.0994962404</v>
+        <v>117810.5491857671</v>
       </c>
     </row>
     <row r="79">
@@ -1572,10 +1572,10 @@
         <v/>
       </c>
       <c r="C79" s="3" t="n">
-        <v>103682.096913032</v>
+        <v>119372.4021174755</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>103682.096913032</v>
+        <v>119372.4021174755</v>
       </c>
     </row>
   </sheetData>
@@ -1589,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>CES0000000001 re-anchored @1989 minus S515-EXT</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>**Period**: 1948-1961</t>
+          <t>**Period**: 1948-2024 (book arm 1948-1989; extension 1990-2024)</t>
         </is>
       </c>
     </row>
@@ -1874,19 +1874,23 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>&gt; **v1.3 note:** Status widened from `book_period_partial_1948_1961` to `book_period_validated`. The panel-backed rebuild (B6) supplies real book-arm data across the full book period 1948-1989 (previously partial 1948-1961); V03 PASS post-rebuild.</t>
+          <t>&gt; **v1.3 note:** Status widened from `book_period_partial_1948_1961` to `book_period_validated`. The panel-backed rebuild (B6) supplies real book-arm data across the full book period 1948-1989; V03 PASS post-rebuild.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>&gt; **REVIEW_2026-07 item D2 note:** The extension was rebuilt (candidate (d), user-ratified — see `Handoffs/REVIEW_2026-07/S515_S516_SEAM_REDESIGN.md`). `TableE3_LaborStatistics.csv` covers the **full book period 1948-1989** (the earlier "1948-1961 only" claim was false and has been removed). The extension now uses `Lu = L − Lp` on the SAME book-anchored total-employment L that S515 uses (BLS CES total nonfarm **including government**), anchored at 1989. The pre-review code used total *private* employment (CES0500000001), which dropped government and drove the −22% Lu seam break.</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1902,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Unproductive labor headcount, computed as the residual: Lu = L_total - Lp_total. Uses the same narrow classification as S515 (TableE3 source).</t>
+          <t>## Definition</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1914,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>## Source / Construction</t>
+          <t>Unproductive labor headcount, computed as the residual: Lu = L_total - Lp_total. Uses the same narrow classification as S515 (TableE3 source).</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1926,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>No separate L01 loader. The P02 processor reads `TableE3_LaborStatistics.csv` directly, extracts the `L_total` and `Lp_total` rows, and computes Lu year-by-year. Both rows are pre-existing in the book table; no extrapolation.</t>
+          <t>## Source / Construction</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1938,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>## Reference</t>
+          <t>No separate L01 loader. The P02 processor reads `TableE3_LaborStatistics.csv` directly, extracts the `L_total` and `Lp_total` rows, and computes Lu year-by-year. Both rows are pre-existing in the book table; no extrapolation.</t>
         </is>
       </c>
     </row>
@@ -1946,23 +1950,19 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Validation benchmarks computed directly from the E.3 row values:</t>
+          <t>## Reference</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>- 1948 = 66,091 - 29,937 = 36,154 thousand</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>- 1961 = 82,827 - 33,615 = 49,212 thousand</t>
+          <t>Validation benchmarks computed directly from the `TableE3` row values `L_total − Lp_total` (Table 5.5 / Appendix F Table F.1 all agree exactly):</t>
         </is>
       </c>
     </row>
@@ -1970,53 +1970,133 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Validator PASS.</t>
+          <t>- 1948 = 58,301 − 32,994 = 25,307 thousand</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>- 1961 = 64,740 − 29,363 = 35,377 thousand</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>## Coverage Caveat</t>
+          <t>- 1989 = 113,511 − 41,148 = 72,363 thousand</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Validator PASS.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Same as S515: 14-year coverage from salvaged E.3 only.</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>## Extension (1990-2024) — Lu = L − Lp on one L basis</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>The extension follows the book's residual rule (FULL_TEXT.md L449: `Lu = L − Lp`), using the SAME single, book-anchored total-employment L as S515 so the identity `L = Lp + Lu` holds at every year including the 1989/1990 seam:</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>- **S516-EXT** = `L_reanchored − S515-EXT`, where `L_reanchored` = BLS CES total nonfarm all employees **including government** (`CES0000000001`, `Inputs/ST2/Inputs/API_Data/BLS/bls_ces_total_nonfarm_all_employees.csv`) multiplicatively re-anchored to the book L (113,511) at 1989, and `S515-EXT` is the published productive Lp (S511 share × L).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>- **S516-COMBINED** = S516-A (book Lu, 1948-1989) spliced to S516-EXT (1990-2024) at 1989.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>This retires the pre-review bug where S516-EXT used total *private* employment (CES0500000001), which dropped government and produced the −22% Lu break. Both arms now share one L basis and one anchor year (1989), so there is no seam discontinuity and no 1962-1989 gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>**Achieved seam** (extension 1990 vs book 1989): Lu **+2.6%** (book 72,363 → EXT 74,222.2); total L **+1.4%** — continuous, within the 5% guard (previously −22% Lu, −19.7% L).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Sample extension values (`data/final/S516.csv`, `series_id == 'S516-EXT'`, thousands): EXT[1995] = 81,435.0, EXT[2010] = 98,142.1, EXT[2024] = 119,372.4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch).*</t>
         </is>
@@ -2585,7 +2665,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>derive</t>
+          <t>derive@1989 (Lu = L - Lp, book method FULL_TEXT L449; L = the SAME book-anchored total-nonfarm-incl-govt L as S515, re-anchored @1989; Lp = published S515-EXT). Single consistent L basis + single anchor → identity holds at every year incl. the seam. Retires the total-PRIVATE-L universe bug (the dominant -22% Lu break driver).</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2713,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>["S515"]</t>
+          <t>["S515-EXT (published Lp)", "Inputs/ST2/Inputs/API_Data/BLS/bls_ces_total_nonfarm_all_employees.csv (CES0000000001)", "data/source/book_tables/TableE3_LaborStatistics.csv:L_total (1989 anchor)"]</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S516.xlsx
+++ b/extenbooks/S516.xlsx
@@ -2030,7 +2030,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>- **S516-EXT** = `L_reanchored − S515-EXT`, where `L_reanchored` = BLS CES total nonfarm all employees **including government** (`CES0000000001`, `Inputs/ST2/Inputs/API_Data/BLS/bls_ces_total_nonfarm_all_employees.csv`) multiplicatively re-anchored to the book L (113,511) at 1989, and `S515-EXT` is the published productive Lp (S511 share × L).</t>
+          <t>- **S516-EXT** = `L_reanchored − S515-EXT`, where `L_reanchored` = BLS CES total nonfarm all employees **including government** (`CES0000000001`, `data/raw/Inputs/API_Data/BLS/bls_ces_total_nonfarm_all_employees.csv`) multiplicatively re-anchored to the book L (113,511) at 1989, and `S515-EXT` is the published productive Lp (S511 share × L).</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>["S515-EXT (published Lp)", "Inputs/ST2/Inputs/API_Data/BLS/bls_ces_total_nonfarm_all_employees.csv (CES0000000001)", "data/source/book_tables/TableE3_LaborStatistics.csv:L_total (1989 anchor)"]</t>
+          <t>["S515-EXT (published Lp)", "data/raw/Inputs/API_Data/BLS/bls_ces_total_nonfarm_all_employees.csv (CES0000000001)", "data/source/book_tables/TableE3_LaborStatistics.csv:L_total (1989 anchor)"]</t>
         </is>
       </c>
     </row>
